--- a/demo/seed-workbook.xlsx
+++ b/demo/seed-workbook.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,10 +464,32 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:55:39.809607+00:00</t>
+          <t>2026-08-31T15:07:29.224363Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>alice</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:07:29.265891Z</t>
         </is>
       </c>
     </row>
@@ -482,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +521,21 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>核心团队</t>
         </is>
       </c>
     </row>
@@ -546,7 +583,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>read,write,admin</t>
+          <t>["read", "write", "admin"]</t>
         </is>
       </c>
     </row>
@@ -563,7 +600,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>read,write,admin</t>
+          <t>["read", "write", "admin"]</t>
         </is>
       </c>
     </row>

--- a/demo/seed-workbook.xlsx
+++ b/demo/seed-workbook.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-31T15:07:29.224363Z</t>
+          <t>2026-08-31T16:28:57.566660Z</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-31T15:07:29.265891Z</t>
+          <t>2026-08-31T16:28:57.603530Z</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,6 +642,31 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ci-check</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[{"type": "shell", "command": "echo ok"}]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>

--- a/demo/seed-workbook.xlsx
+++ b/demo/seed-workbook.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-31T16:28:57.566660Z</t>
+          <t>2026-09-01T15:40:35.119438Z</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-31T16:28:57.603530Z</t>
+          <t>2026-09-01T15:40:35.144122Z</t>
         </is>
       </c>
     </row>

--- a/demo/seed-workbook.xlsx
+++ b/demo/seed-workbook.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-01T15:40:35.119438Z</t>
+          <t>2026-09-04T10:32:05.568693Z</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-01T15:40:35.144122Z</t>
+          <t>2026-09-04T10:32:05.594099Z</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,40 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>["read", "write", "admin"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>["read", "write"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>readonly</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>readonly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>["read"]</t>
         </is>
       </c>
     </row>
@@ -681,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,15 +741,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>pr_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>head_sha</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
@@ -854,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +919,66 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>approval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PR 合并需要至少 1 个审批人</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>approval</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>required_check</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>required-check 工作流需通过</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>required_check</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
